--- a/extracted_data.xlsx
+++ b/extracted_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\temp\Artykuły\ISD Research Agenda cooperation\Publication\Supplementary materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F50AAB-B61C-4B97-8E76-F7D60B48FDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745BB0FB-205B-4536-A9DD-3CD5CCDA1DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="589">
   <si>
     <t>SECONDARY STUDIES ONLY</t>
   </si>
@@ -1438,10 +1438,6 @@
 -(3) "The integration of Generative AI in digital localization enhances efficiency, scalability, and cultural customization, transforming traditional localization processes and enabling hyper-localized content creation."  {Efficiency and scalability [F6]}, {Awareness of user's specifics [F4]}, {Ethical use of GenAI [F4]}, {Proper representation and inclusivity [F4]}
 -(4) "The adoption of Generative AI in global IT management redefines roles and skills, fostering the emergence of hybrid teams where human professionals and AI systems collaborate seamlessly across cultural and regulatory contexts." {Formation of hybrid human-AI teams [F2]}, {The required skills and education [F1]}, {Societal impact of GenAI [F3]}, {Regulations and legal issues related to GenAI [F3]}, {Awareness of user's specifics [F4]}
 -(5)"Generative AI amplifies the sophistication and scale of cyber threats, necessitating the development of advanced AI-powered capabilities for real-time detection, response, and mitigation." {Security and protection [F6]}, {Risks affecting individual users [F1]}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are no standardized structure and main focus in each section(s) contributed by the experts (i.e. it's quite chaotic in my opinion). The authors also pointed out that they have different domain focus.
-In my opinion the paper is weak. </t>
   </si>
   <si>
     <t>Feuerriegel, S., Hartmann, J., Janiesch, C., &amp; Zschech, P. (2024). Generative ai. Business &amp; Information Systems Engineering, 66(1), 111-126.</t>
@@ -5504,6 +5500,9 @@
   </si>
   <si>
     <t>Not retrieved [no extraction!]</t>
+  </si>
+  <si>
+    <t>There are no standardized structure and main focus in each section(s) contributed by the experts (i.e. it's quite chaotic in my opinion). The authors also pointed out that they have different domain focus.</t>
   </si>
 </sst>
 </file>
@@ -6153,7 +6152,7 @@
     </row>
     <row r="3" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>85</v>
@@ -6230,7 +6229,7 @@
     </row>
     <row r="4" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>74</v>
@@ -6307,7 +6306,7 @@
     </row>
     <row r="5" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -6411,7 +6410,7 @@
         <v>108</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>109</v>
@@ -6697,7 +6696,7 @@
         <v>151</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9" t="s">
@@ -6998,10 +6997,10 @@
       <c r="E14" s="20"/>
       <c r="F14" s="20"/>
       <c r="G14" s="20" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
@@ -7178,7 +7177,7 @@
         <v>230</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>231</v>
+        <v>588</v>
       </c>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
@@ -7201,7 +7200,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
@@ -7219,43 +7218,43 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O17" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="S17" s="22" t="s">
+        <v>578</v>
+      </c>
+      <c r="T17" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="U17" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="S17" s="22" t="s">
-        <v>579</v>
-      </c>
-      <c r="T17" s="22" t="s">
-        <v>580</v>
-      </c>
-      <c r="U17" s="1" t="s">
+      <c r="V17" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="V17" s="1" t="s">
+      <c r="W17" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="W17" s="14" t="s">
+      <c r="X17" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="X17" s="14" t="s">
+      <c r="Y17" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
@@ -7278,7 +7277,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D18" s="1">
         <v>41</v>
@@ -7292,16 +7291,16 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="K18" s="1">
         <v>29</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1" t="s">
@@ -7311,31 +7310,31 @@
         <v>48</v>
       </c>
       <c r="P18" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q18" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="T18" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="T18" s="1" t="s">
+      <c r="U18" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="U18" s="1" t="s">
+      <c r="V18" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="V18" s="1" t="s">
+      <c r="W18" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="W18" s="1" t="s">
+      <c r="X18" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
@@ -7359,7 +7358,7 @@
         <v>71</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D19" s="1">
         <v>34</v>
@@ -7373,53 +7372,53 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="K19" s="1">
         <v>38</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1" t="s">
         <v>206</v>
       </c>
       <c r="O19" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="T19" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="U19" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="U19" s="1" t="s">
+      <c r="V19" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="V19" s="1" t="s">
+      <c r="W19" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="W19" s="1" t="s">
+      <c r="X19" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="X19" s="1" t="s">
+      <c r="Y19" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
@@ -7442,7 +7441,7 @@
         <v>67</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D20" s="1">
         <v>28</v>
@@ -7460,43 +7459,43 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O20" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="Q20" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="R20" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="T20" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="T20" s="1" t="s">
+      <c r="U20" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="U20" s="1" t="s">
+      <c r="V20" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="V20" s="1" t="s">
+      <c r="W20" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="W20" s="1" t="s">
+      <c r="X20" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="X20" s="1" t="s">
+      <c r="Y20" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
@@ -7516,10 +7515,10 @@
         <v>114</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>283</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>284</v>
       </c>
       <c r="D21" s="9">
         <v>9</v>
@@ -7534,7 +7533,7 @@
         <v>151</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
@@ -7571,10 +7570,10 @@
         <v>218</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" s="24" t="s">
         <v>285</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>286</v>
       </c>
       <c r="D22" s="9">
         <v>10</v>
@@ -7589,50 +7588,50 @@
         <v>86</v>
       </c>
       <c r="H22" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I22" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="K22" s="9">
         <v>53</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P22" s="9" t="s">
         <v>49</v>
       </c>
       <c r="Q22" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="R22" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="R22" s="9" t="s">
+      <c r="S22" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="S22" s="9" t="s">
-        <v>294</v>
-      </c>
       <c r="T22" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
@@ -7652,10 +7651,10 @@
         <v>32</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>297</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>298</v>
       </c>
       <c r="D23" s="9">
         <v>19</v>
@@ -7670,7 +7669,7 @@
         <v>86</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -7710,7 +7709,7 @@
         <v>65</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D24" s="1">
         <v>13</v>
@@ -7728,38 +7727,38 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>206</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="T24" s="1" t="s">
+      <c r="U24" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="U24" s="1" t="s">
+      <c r="V24" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="V24" s="1" t="s">
+      <c r="W24" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="W24" s="1" t="s">
+      <c r="X24" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -7780,10 +7779,10 @@
         <v>188</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>310</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>311</v>
       </c>
       <c r="D25" s="9">
         <v>8</v>
@@ -7798,38 +7797,38 @@
         <v>86</v>
       </c>
       <c r="H25" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="I25" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="J25" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>314</v>
       </c>
       <c r="K25" s="9">
         <v>19</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="R25" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="R25" s="9" t="s">
+      <c r="S25" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="S25" s="9" t="s">
+      <c r="T25" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="U25" s="9" t="s">
         <v>318</v>
-      </c>
-      <c r="T25" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="U25" s="9" t="s">
-        <v>319</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -7856,7 +7855,7 @@
         <v>63</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D26" s="1">
         <v>27</v>
@@ -7870,53 +7869,53 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="K26" s="1">
         <v>27</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1" t="s">
         <v>206</v>
       </c>
       <c r="O26" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="P26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="Q26" s="1" t="s">
+      <c r="R26" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="T26" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="T26" s="1" t="s">
+      <c r="U26" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="U26" s="1" t="s">
+      <c r="V26" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="V26" s="1" t="s">
+      <c r="W26" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="W26" s="1" t="s">
+      <c r="X26" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="X26" s="1" t="s">
+      <c r="Y26" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
@@ -7939,7 +7938,7 @@
         <v>68</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D27" s="1">
         <v>7</v>
@@ -7953,16 +7952,16 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1" t="s">
@@ -7972,25 +7971,25 @@
         <v>44</v>
       </c>
       <c r="P27" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="T27" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="T27" s="1" t="s">
+      <c r="U27" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="U27" s="1" t="s">
+      <c r="V27" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>152</v>
@@ -7999,7 +7998,7 @@
         <v>152</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
@@ -8022,7 +8021,7 @@
         <v>72</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D28" s="1">
         <v>26</v>
@@ -8036,53 +8035,53 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="K28" s="1">
         <v>14</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1" t="s">
         <v>53</v>
       </c>
       <c r="O28" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="T28" s="1" t="s">
+      <c r="U28" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="U28" s="1" t="s">
+      <c r="V28" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="V28" s="1" t="s">
+      <c r="W28" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="W28" s="1" t="s">
+      <c r="X28" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="X28" s="1" t="s">
+      <c r="Y28" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
@@ -8102,10 +8101,10 @@
         <v>218</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C29" s="23" t="s">
         <v>361</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>362</v>
       </c>
       <c r="D29" s="9">
         <v>17</v>
@@ -8120,19 +8119,19 @@
         <v>108</v>
       </c>
       <c r="H29" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>363</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>364</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
@@ -8140,13 +8139,13 @@
         <v>44</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q29" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="R29" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="R29" s="9" t="s">
-        <v>367</v>
       </c>
       <c r="S29" s="9"/>
       <c r="T29" s="9"/>
@@ -8173,16 +8172,16 @@
         <v>19</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>368</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>369</v>
       </c>
       <c r="D30" s="9">
         <v>9</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>22</v>
@@ -8191,19 +8190,19 @@
         <v>86</v>
       </c>
       <c r="H30" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="I30" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="J30" s="9" t="s">
         <v>372</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>373</v>
       </c>
       <c r="K30" s="9">
         <v>12</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
@@ -8211,30 +8210,30 @@
         <v>49</v>
       </c>
       <c r="P30" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q30" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="Q30" s="9" t="s">
+      <c r="R30" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="R30" s="9" t="s">
+      <c r="S30" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="S30" s="9" t="s">
-        <v>378</v>
-      </c>
       <c r="T30" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="U30" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="X30" s="9"/>
       <c r="Y30" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
@@ -8254,10 +8253,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" s="24" t="s">
         <v>381</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>382</v>
       </c>
       <c r="D31" s="9">
         <v>15</v>
@@ -8272,10 +8271,10 @@
         <v>108</v>
       </c>
       <c r="H31" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>383</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>384</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
@@ -8283,12 +8282,12 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
       <c r="O31" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
@@ -8318,7 +8317,7 @@
         <v>73</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D32" s="1">
         <v>16</v>
@@ -8332,16 +8331,16 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="K32" s="1">
         <v>45</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1" t="s">
@@ -8354,31 +8353,31 @@
         <v>49</v>
       </c>
       <c r="Q32" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="S32" s="1" t="s">
+      <c r="T32" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="T32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="U32" s="1" t="s">
+      <c r="V32" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="V32" s="1" t="s">
+      <c r="W32" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="W32" s="1" t="s">
+      <c r="X32" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="X32" s="1" t="s">
+      <c r="Y32" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
@@ -8395,13 +8394,13 @@
     </row>
     <row r="33" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D33" s="1">
         <v>21</v>
@@ -8415,55 +8414,55 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>206</v>
       </c>
       <c r="O33" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="P33" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="Q33" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="Q33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="S33" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="S33" s="1" t="s">
+      <c r="T33" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="T33" s="1" t="s">
+      <c r="U33" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="U33" s="1" t="s">
+      <c r="V33" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="V33" s="1" t="s">
+      <c r="W33" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="W33" s="1" t="s">
+      <c r="X33" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="X33" s="1" t="s">
+      <c r="Y33" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
@@ -8486,7 +8485,7 @@
         <v>55</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D34" s="1">
         <v>4</v>
@@ -8500,16 +8499,16 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
@@ -8522,31 +8521,31 @@
         <v>125</v>
       </c>
       <c r="Q34" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="R34" s="1" t="s">
+      <c r="S34" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="S34" s="1" t="s">
+      <c r="T34" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="U34" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="V34" s="1" t="s">
+      <c r="W34" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="W34" s="1" t="s">
+      <c r="X34" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="X34" s="1" t="s">
+      <c r="Y34" s="18" t="s">
         <v>430</v>
-      </c>
-      <c r="Y34" s="18" t="s">
-        <v>431</v>
       </c>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
@@ -8566,10 +8565,10 @@
         <v>114</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C35" s="24" t="s">
         <v>432</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>433</v>
       </c>
       <c r="D35" s="9">
         <v>17</v>
@@ -8584,52 +8583,52 @@
         <v>151</v>
       </c>
       <c r="H35" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="I35" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="J35" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="K35" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>436</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>437</v>
       </c>
       <c r="N35" s="9"/>
       <c r="O35" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P35" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q35" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="Q35" s="9" t="s">
+      <c r="R35" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="R35" s="9" t="s">
+      <c r="S35" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="S35" s="9" t="s">
-        <v>441</v>
-      </c>
       <c r="T35" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U35" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="X35" s="9"/>
       <c r="Y35" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
@@ -8652,7 +8651,7 @@
         <v>66</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D36" s="1">
         <v>22</v>
@@ -8670,7 +8669,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>206</v>
@@ -8678,28 +8677,28 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="R36" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="S36" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="S36" s="1" t="s">
+      <c r="T36" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="T36" s="1" t="s">
+      <c r="U36" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="U36" s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="V36" s="1" t="s">
+      <c r="W36" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="W36" s="1" t="s">
+      <c r="X36" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -8717,13 +8716,13 @@
     </row>
     <row r="37" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>454</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>455</v>
       </c>
       <c r="D37" s="1">
         <v>26</v>
@@ -8737,53 +8736,53 @@
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
       <c r="I37" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>49</v>
       </c>
       <c r="O37" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="Q37" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="Q37" s="1" t="s">
+      <c r="R37" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="R37" s="1" t="s">
+      <c r="S37" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="S37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="T37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="U37" s="1" t="s">
+      <c r="V37" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="V37" s="1" t="s">
+      <c r="W37" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="W37" s="1" t="s">
+      <c r="X37" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="X37" s="1" t="s">
+      <c r="Y37" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
@@ -8806,7 +8805,7 @@
         <v>69</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D38" s="1">
         <v>4</v>
@@ -8820,16 +8819,16 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1" t="s">
@@ -8842,31 +8841,31 @@
         <v>46</v>
       </c>
       <c r="Q38" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="S38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="T38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="U38" s="1" t="s">
+      <c r="V38" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="V38" s="1" t="s">
+      <c r="W38" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="W38" s="1" t="s">
+      <c r="X38" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="X38" s="1" t="s">
+      <c r="Y38" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="Y38" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
@@ -8889,7 +8888,7 @@
         <v>54</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D39" s="1">
         <v>12</v>
@@ -8903,53 +8902,53 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K39" s="1">
         <v>20</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="Q39" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="R39" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="R39" s="1" t="s">
+      <c r="S39" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="S39" s="1" t="s">
+      <c r="T39" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="T39" s="1" t="s">
+      <c r="U39" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="U39" s="1" t="s">
+      <c r="V39" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="V39" s="1" t="s">
+      <c r="W39" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="W39" s="1" t="s">
+      <c r="X39" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="X39" s="1" t="s">
+      <c r="Y39" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
@@ -8969,10 +8968,10 @@
         <v>32</v>
       </c>
       <c r="B40" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="24" t="s">
         <v>495</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>496</v>
       </c>
       <c r="D40" s="9">
         <v>16</v>
@@ -8987,7 +8986,7 @@
         <v>151</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
@@ -9024,10 +9023,10 @@
         <v>218</v>
       </c>
       <c r="B41" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="C41" s="24" t="s">
         <v>498</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>499</v>
       </c>
       <c r="D41" s="9">
         <v>10</v>
@@ -9039,22 +9038,22 @@
         <v>22</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="I41" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="J41" s="9" t="s">
         <v>501</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>502</v>
       </c>
       <c r="K41" s="9">
         <v>8</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
@@ -9065,27 +9064,27 @@
         <v>46</v>
       </c>
       <c r="Q41" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="R41" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="R41" s="9" t="s">
+      <c r="S41" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="S41" s="9" t="s">
+      <c r="T41" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="U41" s="9" t="s">
         <v>506</v>
-      </c>
-      <c r="T41" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="U41" s="9" t="s">
-        <v>507</v>
       </c>
       <c r="V41" s="9"/>
       <c r="W41" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="X41" s="9"/>
       <c r="Y41" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
@@ -9105,10 +9104,10 @@
         <v>19</v>
       </c>
       <c r="B42" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C42" s="24" t="s">
         <v>510</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>511</v>
       </c>
       <c r="D42" s="9">
         <v>15</v>
@@ -9123,7 +9122,7 @@
         <v>86</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
@@ -9157,13 +9156,13 @@
     </row>
     <row r="43" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D43" s="1">
         <v>38</v>
@@ -9177,55 +9176,55 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L43" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>206</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="P43" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="Q43" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="Q43" s="1" t="s">
+      <c r="R43" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="T43" s="1" t="s">
+      <c r="U43" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="U43" s="1" t="s">
+      <c r="V43" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="V43" s="1" t="s">
+      <c r="W43" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="W43" s="1" t="s">
+      <c r="X43" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="X43" s="1" t="s">
+      <c r="Y43" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="Y43" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
@@ -9248,7 +9247,7 @@
         <v>76</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D44" s="1">
         <v>12</v>
@@ -9266,7 +9265,7 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>27</v>
@@ -9275,34 +9274,34 @@
         <v>27</v>
       </c>
       <c r="P44" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q44" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="Q44" s="1" t="s">
+      <c r="R44" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="R44" s="1" t="s">
+      <c r="S44" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="S44" s="1" t="s">
+      <c r="T44" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="T44" s="1" t="s">
+      <c r="U44" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="U44" s="1" t="s">
+      <c r="V44" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="V44" s="1" t="s">
+      <c r="W44" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="W44" s="1" t="s">
+      <c r="X44" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="X44" s="1" t="s">
+      <c r="Y44" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
@@ -9319,13 +9318,13 @@
     </row>
     <row r="45" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D45" s="1">
         <v>21</v>
@@ -9343,43 +9342,43 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="Q45" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="R45" s="1" t="s">
+      <c r="S45" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="S45" s="1" t="s">
+      <c r="T45" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="T45" s="1" t="s">
+      <c r="U45" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="U45" s="1" t="s">
+      <c r="V45" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="V45" s="1" t="s">
+      <c r="W45" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="W45" s="1" t="s">
+      <c r="X45" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="X45" s="1" t="s">
+      <c r="Y45" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
@@ -9399,10 +9398,10 @@
         <v>218</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C46" s="25" t="s">
         <v>552</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>553</v>
       </c>
       <c r="D46" s="1">
         <v>22</v>
@@ -9420,43 +9419,43 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>206</v>
       </c>
       <c r="O46" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q46" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="P46" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q46" s="1" t="s">
+      <c r="R46" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="R46" s="1" t="s">
+      <c r="S46" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="S46" s="1" t="s">
+      <c r="T46" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="T46" s="1" t="s">
+      <c r="U46" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="U46" s="1" t="s">
+      <c r="V46" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="V46" s="1" t="s">
+      <c r="W46" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="W46" s="1" t="s">
+      <c r="X46" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="X46" s="1" t="s">
+      <c r="Y46" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
@@ -9476,10 +9475,10 @@
         <v>218</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="C47" s="24" t="s">
         <v>565</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>566</v>
       </c>
       <c r="D47" s="9">
         <v>12</v>
@@ -9494,7 +9493,7 @@
         <v>151</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="9"/>
@@ -9531,10 +9530,10 @@
         <v>188</v>
       </c>
       <c r="B48" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="C48" s="24" t="s">
         <v>568</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>569</v>
       </c>
       <c r="D48" s="9">
         <v>28</v>
@@ -9546,10 +9545,10 @@
         <v>22</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
@@ -9583,13 +9582,13 @@
     </row>
     <row r="49" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
@@ -9597,7 +9596,7 @@
         <v>22</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H49" s="20"/>
       <c r="I49" s="20"/>
@@ -9632,13 +9631,13 @@
     </row>
     <row r="50" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
@@ -9646,7 +9645,7 @@
         <v>22</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H50" s="20"/>
       <c r="I50" s="20"/>
@@ -9681,13 +9680,13 @@
     </row>
     <row r="51" spans="1:37" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
@@ -9695,7 +9694,7 @@
         <v>22</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H51" s="20"/>
       <c r="I51" s="20"/>
